--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 18:03:19</t>
+          <t>2026-08-24 18:12:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 18:03:41</t>
+          <t>2026-08-24 18:12:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 18:03:44</t>
+          <t>2026-08-24 18:12:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 18:03:46</t>
+          <t>2026-08-24 18:12:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:03:49</t>
+          <t>2026-08-24 18:12:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 18:03:50</t>
+          <t>2026-08-24 18:12:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:03:55</t>
+          <t>2026-08-24 18:12:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 18:03:59</t>
+          <t>2026-08-24 18:12:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 18:04:02</t>
+          <t>2026-08-24 18:12:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 18:04:05</t>
+          <t>2026-08-24 18:13:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 18:04:09</t>
+          <t>2026-08-24 18:13:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 18:04:13</t>
+          <t>2026-08-24 18:13:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 18:04:16</t>
+          <t>2026-08-24 18:13:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 18:04:19</t>
+          <t>2026-08-24 18:13:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 18:04:20</t>
+          <t>2026-08-24 18:13:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 18:12:32</t>
+          <t>2026-08-24 18:24:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 18:12:39</t>
+          <t>2026-08-24 18:24:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 18:12:41</t>
+          <t>2026-08-24 18:24:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 18:12:44</t>
+          <t>2026-08-24 18:24:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:12:46</t>
+          <t>2026-08-24 18:24:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 18:12:47</t>
+          <t>2026-08-24 18:24:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:12:52</t>
+          <t>2026-08-24 18:24:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 18:12:56</t>
+          <t>2026-08-24 18:24:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 18:12:59</t>
+          <t>2026-08-24 18:24:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 18:13:03</t>
+          <t>2026-08-24 18:24:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 18:13:06</t>
+          <t>2026-08-24 18:24:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 18:13:10</t>
+          <t>2026-08-24 18:24:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 18:13:13</t>
+          <t>2026-08-24 18:24:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 18:13:17</t>
+          <t>2026-08-24 18:24:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 18:13:17</t>
+          <t>2026-08-24 18:24:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:06</t>
+          <t>2026-08-24 19:02:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:16</t>
+          <t>2026-08-24 19:02:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:18</t>
+          <t>2026-08-24 19:02:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:21</t>
+          <t>2026-08-24 19:02:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:23</t>
+          <t>2026-08-24 19:02:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:24</t>
+          <t>2026-08-24 19:02:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:29</t>
+          <t>2026-08-24 19:02:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:33</t>
+          <t>2026-08-24 19:02:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:36</t>
+          <t>2026-08-24 19:02:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:40</t>
+          <t>2026-08-24 19:02:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:43</t>
+          <t>2026-08-24 19:02:50</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:47</t>
+          <t>2026-08-24 19:02:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:50</t>
+          <t>2026-08-24 19:02:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:53</t>
+          <t>2026-08-24 19:03:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 18:24:53</t>
+          <t>2026-08-24 19:03:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:10</t>
+          <t>2026-08-25 02:34:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:22</t>
+          <t>2026-08-25 02:34:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:25</t>
+          <t>2026-08-25 02:34:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:27</t>
+          <t>2026-08-25 02:34:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:30</t>
+          <t>2026-08-25 02:34:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:31</t>
+          <t>2026-08-25 02:34:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:36</t>
+          <t>2026-08-25 02:34:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:40</t>
+          <t>2026-08-25 02:34:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:43</t>
+          <t>2026-08-25 02:34:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:47</t>
+          <t>2026-08-25 02:34:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:50</t>
+          <t>2026-08-25 02:35:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:54</t>
+          <t>2026-08-25 02:35:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 19:02:57</t>
+          <t>2026-08-25 02:35:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 19:03:01</t>
+          <t>2026-08-25 02:35:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 19:03:01</t>
+          <t>2026-08-25 02:35:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 02:34:17</t>
+          <t>2026-08-25 03:25:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 02:34:32</t>
+          <t>2026-08-25 03:25:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 02:34:35</t>
+          <t>2026-08-25 03:25:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 02:34:37</t>
+          <t>2026-08-25 03:25:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 02:34:40</t>
+          <t>2026-08-25 03:25:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 02:34:40</t>
+          <t>2026-08-25 03:25:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 02:34:45</t>
+          <t>2026-08-25 03:25:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 02:34:49</t>
+          <t>2026-08-25 03:25:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 02:34:53</t>
+          <t>2026-08-25 03:25:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 02:34:56</t>
+          <t>2026-08-25 03:25:54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 02:35:00</t>
+          <t>2026-08-25 03:25:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 02:35:03</t>
+          <t>2026-08-25 03:26:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 02:35:07</t>
+          <t>2026-08-25 03:26:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 02:35:10</t>
+          <t>2026-08-25 03:26:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 02:35:10</t>
+          <t>2026-08-25 03:26:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 03:25:14</t>
+          <t>2026-08-25 03:47:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:25:29</t>
+          <t>2026-08-25 03:47:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 03:25:32</t>
+          <t>2026-08-25 03:47:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 03:25:34</t>
+          <t>2026-08-25 03:47:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 03:25:37</t>
+          <t>2026-08-25 03:47:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 03:25:38</t>
+          <t>2026-08-25 03:47:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 03:25:43</t>
+          <t>2026-08-25 03:48:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 03:25:47</t>
+          <t>2026-08-25 03:48:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 03:25:50</t>
+          <t>2026-08-25 03:48:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 03:25:54</t>
+          <t>2026-08-25 03:48:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 03:25:58</t>
+          <t>2026-08-25 03:48:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 03:26:01</t>
+          <t>2026-08-25 03:48:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 03:26:05</t>
+          <t>2026-08-25 03:48:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 03:26:08</t>
+          <t>2026-08-25 03:48:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 03:26:08</t>
+          <t>2026-08-25 03:48:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 03:47:35</t>
+          <t>2026-08-25 04:30:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:47:49</t>
+          <t>2026-08-25 04:30:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 03:47:52</t>
+          <t>2026-08-25 04:30:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 03:47:54</t>
+          <t>2026-08-25 04:30:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 03:47:57</t>
+          <t>2026-08-25 04:30:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 03:47:57</t>
+          <t>2026-08-25 04:30:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 03:48:03</t>
+          <t>2026-08-25 04:31:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 03:48:06</t>
+          <t>2026-08-25 04:31:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 03:48:10</t>
+          <t>2026-08-25 04:31:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 03:48:13</t>
+          <t>2026-08-25 04:31:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 03:48:17</t>
+          <t>2026-08-25 04:31:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 03:48:20</t>
+          <t>2026-08-25 04:31:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 03:48:24</t>
+          <t>2026-08-25 04:31:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 03:48:27</t>
+          <t>2026-08-25 04:31:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 03:48:27</t>
+          <t>2026-08-25 04:31:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 04:30:34</t>
+          <t>2026-08-25 05:11:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 04:30:51</t>
+          <t>2026-08-25 05:11:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 04:30:53</t>
+          <t>2026-08-25 05:11:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 04:30:56</t>
+          <t>2026-08-25 05:11:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 04:30:59</t>
+          <t>2026-08-25 05:12:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 04:30:59</t>
+          <t>2026-08-25 05:12:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 04:31:05</t>
+          <t>2026-08-25 05:12:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 04:31:08</t>
+          <t>2026-08-25 05:12:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 04:31:12</t>
+          <t>2026-08-25 05:12:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 04:31:15</t>
+          <t>2026-08-25 05:12:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 04:31:19</t>
+          <t>2026-08-25 05:12:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 04:31:22</t>
+          <t>2026-08-25 05:12:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 04:31:26</t>
+          <t>2026-08-25 05:12:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 04:31:29</t>
+          <t>2026-08-25 05:12:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 04:31:29</t>
+          <t>2026-08-25 05:12:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 05:11:28</t>
+          <t>2026-08-25 05:32:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:11:54</t>
+          <t>2026-08-25 05:32:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 05:11:56</t>
+          <t>2026-08-25 05:32:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 05:11:59</t>
+          <t>2026-08-25 05:32:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 05:12:02</t>
+          <t>2026-08-25 05:32:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 05:12:02</t>
+          <t>2026-08-25 05:32:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 05:12:08</t>
+          <t>2026-08-25 05:32:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 05:12:11</t>
+          <t>2026-08-25 05:32:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 05:12:14</t>
+          <t>2026-08-25 05:32:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 05:12:18</t>
+          <t>2026-08-25 05:32:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 05:12:21</t>
+          <t>2026-08-25 05:32:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 05:12:25</t>
+          <t>2026-08-25 05:32:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 05:12:28</t>
+          <t>2026-08-25 05:33:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 05:12:31</t>
+          <t>2026-08-25 05:33:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 05:12:31</t>
+          <t>2026-08-25 05:33:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 05:32:11</t>
+          <t>2026-08-25 05:47:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:32:27</t>
+          <t>2026-08-25 05:48:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 05:32:29</t>
+          <t>2026-08-25 05:48:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 05:32:32</t>
+          <t>2026-08-25 05:48:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 05:32:34</t>
+          <t>2026-08-25 05:48:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 05:32:35</t>
+          <t>2026-08-25 05:48:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 05:32:40</t>
+          <t>2026-08-25 05:48:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 05:32:44</t>
+          <t>2026-08-25 05:48:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 05:32:47</t>
+          <t>2026-08-25 05:48:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 05:32:51</t>
+          <t>2026-08-25 05:48:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 05:32:54</t>
+          <t>2026-08-25 05:48:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 05:32:58</t>
+          <t>2026-08-25 05:48:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 05:33:01</t>
+          <t>2026-08-25 05:48:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 05:33:05</t>
+          <t>2026-08-25 05:48:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 05:33:05</t>
+          <t>2026-08-25 05:48:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 05:47:58</t>
+          <t>2026-08-25 05:53:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:11</t>
+          <t>2026-08-25 05:53:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:13</t>
+          <t>2026-08-25 05:53:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:16</t>
+          <t>2026-08-25 05:53:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:18</t>
+          <t>2026-08-25 05:53:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:19</t>
+          <t>2026-08-25 05:54:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:24</t>
+          <t>2026-08-25 05:54:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:28</t>
+          <t>2026-08-25 05:54:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:32</t>
+          <t>2026-08-25 05:54:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:35</t>
+          <t>2026-08-25 05:54:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:39</t>
+          <t>2026-08-25 05:54:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:42</t>
+          <t>2026-08-25 05:54:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:46</t>
+          <t>2026-08-25 05:54:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:49</t>
+          <t>2026-08-25 05:54:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 05:48:49</t>
+          <t>2026-08-25 05:54:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 05:53:45</t>
+          <t>2026-08-25 06:13:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:53:52</t>
+          <t>2026-08-25 06:13:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 05:53:54</t>
+          <t>2026-08-25 06:13:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 05:53:57</t>
+          <t>2026-08-25 06:13:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 05:53:59</t>
+          <t>2026-08-25 06:13:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 05:54:00</t>
+          <t>2026-08-25 06:13:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 05:54:05</t>
+          <t>2026-08-25 06:13:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 05:54:09</t>
+          <t>2026-08-25 06:13:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 05:54:12</t>
+          <t>2026-08-25 06:13:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 05:54:16</t>
+          <t>2026-08-25 06:13:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 05:54:19</t>
+          <t>2026-08-25 06:13:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 05:54:23</t>
+          <t>2026-08-25 06:13:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 05:54:26</t>
+          <t>2026-08-25 06:13:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 05:54:30</t>
+          <t>2026-08-25 06:14:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 05:54:30</t>
+          <t>2026-08-25 06:14:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:12</t>
+          <t>2026-08-25 06:34:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:24</t>
+          <t>2026-08-25 06:34:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:27</t>
+          <t>2026-08-25 06:34:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:29</t>
+          <t>2026-08-25 06:34:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:32</t>
+          <t>2026-08-25 06:34:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:33</t>
+          <t>2026-08-25 06:34:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:38</t>
+          <t>2026-08-25 06:34:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:42</t>
+          <t>2026-08-25 06:34:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:45</t>
+          <t>2026-08-25 06:34:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:49</t>
+          <t>2026-08-25 06:34:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:52</t>
+          <t>2026-08-25 06:34:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:56</t>
+          <t>2026-08-25 06:34:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 06:13:59</t>
+          <t>2026-08-25 06:35:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 06:14:03</t>
+          <t>2026-08-25 06:35:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 06:14:03</t>
+          <t>2026-08-25 06:35:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 06:34:20</t>
+          <t>2026-08-25 07:00:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 06:34:26</t>
+          <t>2026-08-25 07:01:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 06:34:29</t>
+          <t>2026-08-25 07:01:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 06:34:32</t>
+          <t>2026-08-25 07:01:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 06:34:34</t>
+          <t>2026-08-25 07:01:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 06:34:35</t>
+          <t>2026-08-25 07:01:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 06:34:40</t>
+          <t>2026-08-25 07:01:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 06:34:43</t>
+          <t>2026-08-25 07:01:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 06:34:47</t>
+          <t>2026-08-25 07:01:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 06:34:51</t>
+          <t>2026-08-25 07:01:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 06:34:54</t>
+          <t>2026-08-25 07:01:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 06:34:58</t>
+          <t>2026-08-25 07:01:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 06:35:01</t>
+          <t>2026-08-25 07:01:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 06:35:05</t>
+          <t>2026-08-25 07:01:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 06:35:05</t>
+          <t>2026-08-25 07:01:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 07:00:59</t>
+          <t>2026-08-25 07:27:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:14</t>
+          <t>2026-08-25 07:27:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:16</t>
+          <t>2026-08-25 07:27:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:19</t>
+          <t>2026-08-25 07:27:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:22</t>
+          <t>2026-08-25 07:27:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:22</t>
+          <t>2026-08-25 07:27:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:27</t>
+          <t>2026-08-25 07:27:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:31</t>
+          <t>2026-08-25 07:27:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:34</t>
+          <t>2026-08-25 07:27:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:38</t>
+          <t>2026-08-25 07:27:50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:41</t>
+          <t>2026-08-25 07:27:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:45</t>
+          <t>2026-08-25 07:27:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:48</t>
+          <t>2026-08-25 07:28:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:52</t>
+          <t>2026-08-25 07:28:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 07:01:52</t>
+          <t>2026-08-25 07:28:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 07:27:22</t>
+          <t>2026-08-25 07:54:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 07:27:27</t>
+          <t>2026-08-25 07:54:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 07:27:29</t>
+          <t>2026-08-25 07:54:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 07:27:31</t>
+          <t>2026-08-25 07:54:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 07:27:34</t>
+          <t>2026-08-25 07:54:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 07:27:34</t>
+          <t>2026-08-25 07:54:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 07:27:39</t>
+          <t>2026-08-25 07:55:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 07:27:43</t>
+          <t>2026-08-25 07:55:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 07:27:46</t>
+          <t>2026-08-25 07:55:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 07:27:50</t>
+          <t>2026-08-25 07:55:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 07:27:53</t>
+          <t>2026-08-25 07:55:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 07:27:57</t>
+          <t>2026-08-25 07:55:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 07:28:00</t>
+          <t>2026-08-25 07:55:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 07:28:03</t>
+          <t>2026-08-25 07:55:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 07:28:03</t>
+          <t>2026-08-25 07:55:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 07:54:39</t>
+          <t>2026-08-25 08:23:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 07:54:50</t>
+          <t>2026-08-25 08:23:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 07:54:52</t>
+          <t>2026-08-25 08:23:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 07:54:55</t>
+          <t>2026-08-25 08:23:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 07:54:57</t>
+          <t>2026-08-25 08:23:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 07:54:57</t>
+          <t>2026-08-25 08:23:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 07:55:03</t>
+          <t>2026-08-25 08:23:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 07:55:06</t>
+          <t>2026-08-25 08:23:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 07:55:10</t>
+          <t>2026-08-25 08:24:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 07:55:13</t>
+          <t>2026-08-25 08:24:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 07:55:16</t>
+          <t>2026-08-25 08:24:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 07:55:20</t>
+          <t>2026-08-25 08:24:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 07:55:23</t>
+          <t>2026-08-25 08:24:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 07:55:26</t>
+          <t>2026-08-25 08:24:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 07:55:27</t>
+          <t>2026-08-25 08:24:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/test-report/Selenium_Live_Execution_Report.xlsx
+++ b/test-report/Selenium_Live_Execution_Report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 08:23:23</t>
+          <t>2026-08-25 08:32:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 08:23:39</t>
+          <t>2026-08-25 08:33:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 08:23:42</t>
+          <t>2026-08-25 08:33:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 08:23:44</t>
+          <t>2026-08-25 08:33:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 08:23:47</t>
+          <t>2026-08-25 08:33:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 08:23:47</t>
+          <t>2026-08-25 08:33:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 08:23:53</t>
+          <t>2026-08-25 08:33:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 08:23:56</t>
+          <t>2026-08-25 08:33:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 08:24:00</t>
+          <t>2026-08-25 08:33:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 08:24:03</t>
+          <t>2026-08-25 08:33:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 08:24:07</t>
+          <t>2026-08-25 08:33:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 08:24:10</t>
+          <t>2026-08-25 08:33:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 08:24:14</t>
+          <t>2026-08-25 08:33:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 08:24:18</t>
+          <t>2026-08-25 08:33:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 08:24:18</t>
+          <t>2026-08-25 08:33:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
